--- a/open/Trans_acc/Gear_Designer/gear.xlsx
+++ b/open/Trans_acc/Gear_Designer/gear.xlsx
@@ -446,7 +446,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40.0000</t>
+          <t>20.0000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -466,7 +466,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.2500</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -568,7 +568,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>40.0000</t>
+          <t>20.0000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.0000</t>
+          <t>1.2500</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20.0000</t>
+          <t>10.0000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>42.0000</t>
+          <t>22.0000</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>38.0000</t>
+          <t>17.5000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>37.5877</t>
+          <t>18.7939</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>125.6637</t>
+          <t>62.8319</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.0000</t>
+          <t>11.0000</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>19.0000</t>
+          <t>8.7500</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0785</t>
+          <t>0.1571</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>18.7939</t>
+          <t>9.3969</t>
         </is>
       </c>
     </row>
@@ -744,7 +744,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>131.9469</t>
+          <t>69.1150</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>119.3805</t>
+          <t>54.9779</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0785</t>
+          <t>0.1571</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>118.0853</t>
+          <t>59.0426</t>
         </is>
       </c>
     </row>
@@ -806,7 +806,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2.0000</t>
+          <t>2.2500</t>
         </is>
       </c>
     </row>
@@ -818,7 +818,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.1571</t>
+          <t>0.3142</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.0000</t>
+          <t>0.2500</t>
         </is>
       </c>
     </row>
